--- a/data-exel/products_export.xlsx
+++ b/data-exel/products_export.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>LG</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>200.00</t>
+  </si>
+  <si>
+    <t>super cool watch</t>
   </si>
 </sst>
 </file>
@@ -442,7 +451,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -480,7 +489,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -497,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>10</v>
@@ -514,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -531,7 +540,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -548,10 +557,27 @@
         <v>18</v>
       </c>
       <c r="D6" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
